--- a/data_out/country_spreadsheets/Finland.xlsx
+++ b/data_out/country_spreadsheets/Finland.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>112.99</v>
       </c>
+      <c r="X2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>137.99</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>112.99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>43.33</v>
       </c>
+      <c r="X3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>120.24</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>136.88</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>2.46</v>
       </c>
+      <c r="X4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>3.09</v>
       </c>
+      <c r="X5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>52.35</v>
       </c>
+      <c r="X6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>178.79</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>176.63</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>115.14</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52.35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>9.59</v>
       </c>
+      <c r="X7" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>10.28</v>
       </c>
+      <c r="X8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>139.08</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>149.51</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10.28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>44.69</v>
       </c>
+      <c r="X9" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>161.86</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>44.69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>56.13</v>
       </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>159.98</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>187.79</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>154.37</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>107.76</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>56.13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>30.08</v>
       </c>
+      <c r="X11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>139.03</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>103.46</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>158.89</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30.08</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>51.25</v>
       </c>
+      <c r="X12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>121</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>165.02</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>120.44</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>153.71</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>207.65</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>51.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>43.26</v>
       </c>
+      <c r="X13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>61.72</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>43.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>142.62</v>
       </c>
+      <c r="X14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>139.77</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>173.96</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>142.62</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>165.81</v>
       </c>
+      <c r="X15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>165.81</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>66.25</v>
       </c>
+      <c r="X16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>177.41</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>66.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>87.7</v>
       </c>
+      <c r="X17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>87.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>78.84999999999999</v>
       </c>
+      <c r="X18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>78.84999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>22.77</v>
       </c>
+      <c r="X19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>22.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2005,6 +3008,57 @@
         <v>45.36</v>
       </c>
       <c r="W20" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>121.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>83.69</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>114.54</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>127.77</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="AN20" t="n">
         <v>12.07</v>
       </c>
     </row>
